--- a/artfynd/A 56759-2023 artfynd.xlsx
+++ b/artfynd/A 56759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137495355</v>
+        <v>137498063</v>
       </c>
       <c r="B3" t="n">
-        <v>61596</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106670</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,20 +824,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 39820-26 v. Koholma, Sk</t>
+          <t>Koholma Aggarp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403317</v>
+        <v>403300</v>
       </c>
       <c r="R3" t="n">
-        <v>6212914</v>
+        <v>6212909</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,56 +890,55 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137495355</t>
+          <t>https://artportalen.se/Sighting/137498063</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137495353</v>
+        <v>137495355</v>
       </c>
       <c r="B4" t="n">
-        <v>106622</v>
+        <v>61596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221157</v>
+        <v>106670</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403310</v>
+        <v>403317</v>
       </c>
       <c r="R4" t="n">
-        <v>6212911</v>
+        <v>6212914</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,6 +1002,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,6 +1019,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137495355</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137495353</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106622</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 39820-26 v. Koholma, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>403310</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6212911</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Färingtofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137495353</t>
         </is>
@@ -1024,6 +1141,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56759-2023 artfynd.xlsx
+++ b/artfynd/A 56759-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137495352</v>
       </c>
       <c r="B2" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137498063</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137495355</v>
       </c>
       <c r="B4" t="n">
-        <v>61596</v>
+        <v>61600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>137495353</v>
       </c>
       <c r="B5" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
